--- a/data/trans_dic/IP31KM02_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM02_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>62,1%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>55,9; 71,17</t>
+          <t>45,94; 68,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42,14; 66,53</t>
+          <t>56,32; 71,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50,21; 65,59</t>
+          <t>54,41; 67,52</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>67,15%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>54,41; 68,37</t>
+          <t>62,12; 74,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>59,9; 72,1</t>
+          <t>58,94; 71,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59,69; 68,87</t>
+          <t>62,37; 71,12</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>52,24%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27,5; 55,91</t>
+          <t>43,86; 59,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44,41; 59,21</t>
+          <t>44,97; 59,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,86; 54,93</t>
+          <t>47,04; 57,79</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,77%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>49,91; 62,89</t>
+          <t>48,74; 62,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>48,22; 61,46</t>
+          <t>49,91; 62,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50,6; 59,9</t>
+          <t>50,72; 60,26</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>59,67%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>48,81; 60,54</t>
+          <t>56,0; 63,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>54,2; 61,97</t>
+          <t>56,07; 62,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53,5; 60,05</t>
+          <t>57,05; 62,33</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>119</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>73121</t>
+          <t>74030</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>77235</t>
+          <t>75941</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>150357</t>
+          <t>149971</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>63864; 81318</t>
+          <t>56458; 84496</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>57655; 91017</t>
+          <t>66795; 84616</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>126072; 164684</t>
+          <t>131394; 163062</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>177</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>115219</t>
+          <t>158665</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>164658</t>
+          <t>117886</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>279878</t>
+          <t>276550</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>101258; 127243</t>
+          <t>143641; 171741</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>148259; 178454</t>
+          <t>106444; 129298</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>258851; 298647</t>
+          <t>256852; 292913</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>118</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>85344</t>
+          <t>86383</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>95026</t>
+          <t>81616</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>180370</t>
+          <t>167999</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>51774; 105256</t>
+          <t>73030; 99386</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>81307; 108401</t>
+          <t>69725; 92556</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>136878; 203993</t>
+          <t>151253; 185841</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>92635</t>
+          <t>91756</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>96701</t>
+          <t>92377</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>189336</t>
+          <t>184133</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>82105; 103464</t>
+          <t>80984; 103505</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>85501; 108979</t>
+          <t>81839; 103257</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>172962; 204761</t>
+          <t>167461; 198931</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>544</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>366321</t>
+          <t>410834</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>433620</t>
+          <t>367819</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>799941</t>
+          <t>778653</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>318794; 395379</t>
+          <t>384652; 434676</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>403613; 461505</t>
+          <t>346615; 386977</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>747858; 839350</t>
+          <t>744514; 813442</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM02_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM02_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman una 2ª pieza de fruta todos los días (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>60,24%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>64,03%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>62,1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>45,94; 68,75</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>56,32; 71,35</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>54,41; 67,52</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>68,61%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>65,28%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>67,15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>62,12; 74,27</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>58,94; 71,6</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>62,37; 71,12</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>51,87%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>52,64%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>52,24%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>43,86; 59,68</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>44,97; 59,7</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>47,04; 57,79</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>55,22%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>56,33%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>55,77%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>48,74; 62,29</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>49,91; 62,97</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>50,72; 60,26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>59,82%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>59,5%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>59,67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>56,0; 63,29</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>56,07; 62,6</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>57,05; 62,33</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.6023797764805199</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.6403186002308129</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.6210115271945741</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>74030</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>75941</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>149971</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.4593940186429546</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.5632044460463773</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.5440868325289208</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>56458; 84496</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>66795; 84616</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>131394; 163062</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.6875393478968375</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.7134693674979595</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.6752224471723639</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>399</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.6861462829577736</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.6527711659872851</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.6715109789388637</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>158665</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>117886</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>276550</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.6211745559508928</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.5894135448964399</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.6236805934482121</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>143641; 171741</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>106444; 129298</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>256852; 292913</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.7426933865971306</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.7159620515335962</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.7112418726423153</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.5187459020182781</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.5264256942365769</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.5224486668716858</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>86383</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>81616</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>167999</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.4385604169482596</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.4497291656043069</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.4703716613454945</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>73030; 99386</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>69725; 92556</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>151253; 185841</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.5968318629860228</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.5969872449003448</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.5779363111591819</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.5521999536714406</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.5633455266115203</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.5577358411735085</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>91756</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>92377</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>184133</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.4873714943641575</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.4990802396026154</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.5072362391632242</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>80984; 103505</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>81839; 103257</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167461; 198931</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.6229072857046291</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.6296966951439008</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.6025579983680327</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1112</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.5981650478493215</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.5949764411916042</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.5966545698772431</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>410834</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>367819</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>778653</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.5600451767137267</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.5606765139598505</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.5704954957137994</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>384652; 434676</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>346615; 386977</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>744514; 813442</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.6328778798302169</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.6259662197340933</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.6233121690315467</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman una 2ª pieza de fruta todos los días (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>119</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>74030</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>75941</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>149971</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>56458</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>66795</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>131394</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>84496</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>84616</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>163062</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>222</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>177</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>158665</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>117886</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>276550</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>143641</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>106444</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>256852</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>171741</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>129298</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>292913</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>116</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>118</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>86383</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>81616</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>167999</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>73030</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>69725</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>151253</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>99386</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>92556</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>185841</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>91756</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>92377</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>184133</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>80984</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>81839</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>167461</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>103505</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>103257</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>198931</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>568</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>544</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>410834</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>367819</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>778653</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>384652</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>346615</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>744514</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>434676</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>386977</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>813442</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>